--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/ALASKA_2016.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2016/ALASKA_2016.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Total</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Total</t>
@@ -470,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Total</t>
@@ -514,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -529,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -545,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -558,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -571,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Total</t>
@@ -586,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -602,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Ocuilan</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -666,7 +726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C21">
@@ -677,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -708,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -721,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -752,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Aquila</t>
@@ -765,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Cuitzeo</t>
@@ -778,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -791,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -804,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -835,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Yogana</t>
@@ -848,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Total</t>
@@ -879,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -892,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -923,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Total</t>
@@ -954,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -985,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1016,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1029,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -1042,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Jerez</t>
@@ -1055,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C48">
@@ -1068,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1091,76 +1251,6 @@
       </c>
       <c r="D50">
         <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 814,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Marzo de 2017</t>
-        </is>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 1,114,005</t>
-        </is>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>Junio de 2016</t>
-        </is>
       </c>
     </row>
   </sheetData>
